--- a/data/2026_F_Mid_History_word.xlsx
+++ b/data/2026_F_Mid_History_word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\word-tester\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F15C5E1-E709-4F93-9D4B-D0039023792C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0B1AFD-C774-4177-BA83-4D622886CFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D74F88DA-524E-4131-9278-ADECDDB98FFE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t>용어 (Terms)</t>
   </si>
@@ -520,13 +520,97 @@
   </si>
   <si>
     <t>Woven cloth.</t>
+  </si>
+  <si>
+    <t>to get possession of something[14][17]</t>
+  </si>
+  <si>
+    <t>the power to give orders or make decisions[14][17]</t>
+  </si>
+  <si>
+    <t>to invite the start of a fight, contest, or competition[14][17]</t>
+  </si>
+  <si>
+    <t>important or significant[14][17]</t>
+  </si>
+  <si>
+    <t>to divide into shares and deliver to different people[14][17]</t>
+  </si>
+  <si>
+    <t>to separate from others[14][17]</t>
+  </si>
+  <si>
+    <t>involving physical effort[14][17]</t>
+  </si>
+  <si>
+    <t>to depend on someone or something[14][17]</t>
+  </si>
+  <si>
+    <t>to have a home in a particular place[14][17]</t>
+  </si>
+  <si>
+    <t>the part an individual fulfills in society[14][17]</t>
+  </si>
+  <si>
+    <t>to unite or bring together in one unit[14][17]</t>
+  </si>
+  <si>
+    <t>one of a kind; different from all others[14][17]</t>
+  </si>
+  <si>
+    <t>acquire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>authority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>challenge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crucial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isolate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rely</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,6 +635,19 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -560,12 +657,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDADCE0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDADCE0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDADCE0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDADCE0"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -574,7 +686,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -583,6 +695,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -918,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF918F20-6B4A-4308-93F6-F9BDA418B1BD}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.875" customWidth="1"/>
@@ -1245,12 +1363,108 @@
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
